--- a/NTu/aggregate_Kabianga_results.xlsx
+++ b/NTu/aggregate_Kabianga_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,12 +417,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Tea</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Napier</t>
         </is>
@@ -446,322 +434,322 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53.06250952453047</v>
+        <v>36.3875035436673</v>
       </c>
       <c r="B3" t="n">
-        <v>43.43301190272391</v>
+        <v>26.76273709971868</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27.86542293427128</v>
+        <v>19.06866769860454</v>
       </c>
       <c r="B4" t="n">
-        <v>22.78124305828052</v>
+        <v>14.00824604062083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17.47107172870497</v>
+        <v>11.89391140140968</v>
       </c>
       <c r="B5" t="n">
-        <v>14.24062824495023</v>
+        <v>8.711829115333728</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11.90445258000081</v>
+        <v>8.029799439261035</v>
       </c>
       <c r="B6" t="n">
-        <v>9.651383173046591</v>
+        <v>5.850694196403428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.83879615889019</v>
+        <v>5.88435803486756</v>
       </c>
       <c r="B7" t="n">
-        <v>7.111554989885978</v>
+        <v>4.255493652976995</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7.084908790959308</v>
+        <v>4.643377277509217</v>
       </c>
       <c r="B8" t="n">
-        <v>5.648699830538182</v>
+        <v>3.32788088752199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.026428122357079</v>
+        <v>3.884364188063638</v>
       </c>
       <c r="B9" t="n">
-        <v>4.758475489778609</v>
+        <v>2.757133492225421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.341141654116892</v>
+        <v>3.3860856411064</v>
       </c>
       <c r="B10" t="n">
-        <v>4.176984870022125</v>
+        <v>2.380363381338308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4.859637594433953</v>
+        <v>3.03194201101339</v>
       </c>
       <c r="B11" t="n">
-        <v>3.76529097599825</v>
+        <v>2.111582216341456</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4.492416684661531</v>
+        <v>2.760112889734557</v>
       </c>
       <c r="B12" t="n">
-        <v>3.449847368165516</v>
+        <v>1.905089267928735</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4.191943005240674</v>
+        <v>2.537581206453964</v>
       </c>
       <c r="B13" t="n">
-        <v>3.191470385035563</v>
+        <v>1.736386130134785</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.932775931433014</v>
+        <v>2.346521966988353</v>
       </c>
       <c r="B14" t="n">
-        <v>2.96908683430234</v>
+        <v>1.592170644909615</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.701134793983542</v>
+        <v>2.177146238647798</v>
       </c>
       <c r="B15" t="n">
-        <v>2.771193075908945</v>
+        <v>1.465073045596673</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3.48940716915042</v>
+        <v>2.023931077048621</v>
       </c>
       <c r="B16" t="n">
-        <v>2.59135749054245</v>
+        <v>1.350880769100565</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3.293254970777468</v>
+        <v>1.883630267823037</v>
       </c>
       <c r="B17" t="n">
-        <v>2.425848744029963</v>
+        <v>1.247072859458314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3.11008778453728</v>
+        <v>1.754223183421407</v>
       </c>
       <c r="B18" t="n">
-        <v>2.272383459948448</v>
+        <v>1.152044633354118</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.938256498311967</v>
+        <v>1.634358342797616</v>
       </c>
       <c r="B19" t="n">
-        <v>2.129463951340786</v>
+        <v>1.064696564047329</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2.776626666464333</v>
+        <v>1.523058052997139</v>
       </c>
       <c r="B20" t="n">
-        <v>1.996027215288701</v>
+        <v>0.9842155140293301</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2.624352188021911</v>
+        <v>1.4195609450136</v>
       </c>
       <c r="B21" t="n">
-        <v>1.871258236371238</v>
+        <v>0.9099576439186213</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2.480754723993433</v>
+        <v>1.323237411663039</v>
       </c>
       <c r="B22" t="n">
-        <v>1.754490097278013</v>
+        <v>0.8413851349222909</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2.345258982010383</v>
+        <v>1.23354364309777</v>
       </c>
       <c r="B23" t="n">
-        <v>1.645150005640033</v>
+        <v>0.7780314477385654</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2.217357559798705</v>
+        <v>1.149996145101644</v>
       </c>
       <c r="B24" t="n">
-        <v>1.542729653545067</v>
+        <v>0.7194817615399719</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2.09659146339534</v>
+        <v>1.072157168926988</v>
       </c>
       <c r="B25" t="n">
-        <v>1.446768511571709</v>
+        <v>0.6653615305278416</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.982538968839717</v>
+        <v>0.9996259913626062</v>
       </c>
       <c r="B26" t="n">
-        <v>1.356844033844794</v>
+        <v>0.6153294195067692</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1.8748089529902</v>
+        <v>0.9320333650679942</v>
       </c>
       <c r="B27" t="n">
-        <v>1.272565587475109</v>
+        <v>0.569072635963162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1.773036643353445</v>
+        <v>0.8690377170993268</v>
       </c>
       <c r="B28" t="n">
-        <v>1.193570417642841</v>
+        <v>0.5263036042615331</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.676880699803836</v>
+        <v>0.8103223383415354</v>
       </c>
       <c r="B29" t="n">
-        <v>1.119520750817675</v>
+        <v>0.4867574184351658</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1.586021049705617</v>
+        <v>0.755593158168594</v>
       </c>
       <c r="B30" t="n">
-        <v>1.050101556854078</v>
+        <v>0.4501897699353066</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1.500157166813243</v>
+        <v>0.7045768848846924</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9850187120222907</v>
+        <v>0.4163751845230242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1.419006626629923</v>
+        <v>0.6570193913115409</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9239974223410883</v>
+        <v>0.3851054758005337</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.342303846384209</v>
+        <v>0.6126842775366205</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8667808289429738</v>
+        <v>0.3561883620380399</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1.269798957960814</v>
+        <v>0.571351571011841</v>
       </c>
       <c r="B34" t="n">
-        <v>0.8131287504965741</v>
+        <v>0.32944621406007</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.201256783611676</v>
+        <v>0.5328165394394091</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7628165356410032</v>
+        <v>0.3047149134597997</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.136455895917232</v>
+        <v>0.4968886002591783</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7156340081411846</v>
+        <v>0.2818428068132922</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.075187749811266</v>
+        <v>0.4633903152397731</v>
       </c>
       <c r="B37" t="n">
-        <v>0.6713844929092309</v>
+        <v>0.2606897452514261</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.017255878090137</v>
+        <v>0.432156461430542</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6298839141331504</v>
+        <v>0.2411262009535259</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.9624751438944751</v>
+        <v>0.4030331714108921</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5909599586330027</v>
+        <v>0.2230324535436949</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.9106710449285463</v>
+        <v>0.3758771368579943</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5544512987224314</v>
+        <v>0.2062978403280956</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8616790650242431</v>
+        <v>0.3505548702448304</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5202068696679257</v>
+        <v>0.1908200650213748</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8153440692088102</v>
+        <v>0.3269420200232863</v>
       </c>
       <c r="B42" t="n">
-        <v>0.4880851974173292</v>
+        <v>0.176504560168335</v>
       </c>
     </row>
   </sheetData>
